--- a/docs/design/ACSMS-SCR-013/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者履歴情報画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-013/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者履歴情報画面_v1.0.xlsx
@@ -9305,7 +9305,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">設計仕様の履歴一覧カラム（ID / 履歴番号 / 管理支店 / 支店名 / 組合員コード / 購読者名 / 購読者住所 / 連絡先１ / 連絡先２ / メールアドレス / メールマガジンフラグ（コード名称）/ 生年 / 性別 / 購読者層分類 / 農業者分類 / 購読部数 / 前回購読部数 / 配達先氏名 / 配達先郵便 / 前回配達先郵便 / 配達先住所 / 前回配達先住所 / 販売店名 / 前回販売店名 / 手続種別 / 購読開始日 / 購読中止日 / 変更適用日 / 最新データフラグ / 増減報告フラグ / 新規フラグ / 解約フラグ / 引落口座貯金種目 / 引落元口座店舗コード / 引落元口座店舗名 / 引落口座番号 / 引落口座名義）が表示されること
+            <t xml:space="preserve">設計仕様の履歴一覧カラム（ID / 履歴番号 / 管理支店 / 支店名 / 組合員コード / 購読者名 / 購読者住所 / 連絡先１ / 連絡先２ / メールアドレス / メールマガジンフラグ / 生年 / 性別 / 購読者層分類 / 農業者分類 / 購読部数 / 前回購読部数 / 配達先氏名 / 配達先郵便 / 前回配達先郵便 / 配達先住所 / 前回配達先住所 / 販売店名 / 前回販売店名 / 手続種別 / 購読開始日 / 購読中止日 / 変更適用日 / 最新データフラグ / 増減報告フラグ / 新規フラグ / 解約フラグ / 引落口座貯金種目 / 引落元口座店舗コード / 引落元口座店舗名 / 引落口座番号 / 引落口座名義）が表示されること
 </t>
           </r>
           <r>

--- a/docs/design/ACSMS-SCR-013/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者履歴情報画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-013/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者履歴情報画面_v1.0.xlsx
@@ -6346,7 +6346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ49"/>
+  <dimension ref="A1:BQ57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9305,7 +9305,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">設計仕様の履歴一覧カラム（ID / 履歴番号 / 管理支店 / 支店名 / 組合員コード / 購読者名 / 購読者住所 / 連絡先１ / 連絡先２ / メールアドレス / メールマガジンフラグ / 生年 / 性別 / 購読者層分類 / 農業者分類 / 購読部数 / 前回購読部数 / 配達先氏名 / 配達先郵便 / 前回配達先郵便 / 配達先住所 / 前回配達先住所 / 販売店名 / 前回販売店名 / 手続種別 / 購読開始日 / 購読中止日 / 変更適用日 / 最新データフラグ / 増減報告フラグ / 新規フラグ / 解約フラグ / 引落口座貯金種目 / 引落元口座店舗コード / 引落元口座店舗名 / 引落口座番号 / 引落口座名義）が表示されること
+            <t xml:space="preserve">設計仕様の履歴一覧カラム（ID / 履歴番号 / 購読種別 / 電子版読者種別 / 電子申込承認ステータス / 管理支店 / 支店名 / 組合員コード / 購読者名 / 購読者住所 / 連絡先１ / 連絡先２ / メールアドレス / メールマガジンフラグ / 生年 / 性別 / 購読者層分類 / 農業者分類 / 購読部数 / 前回購読部数 / 配達先氏名 / 配達先郵便 / 前回配達先郵便 / 配達先住所 / 前回配達先住所 / 販売店名 / 前回販売店名 / 手続種別 / 購読開始日 / 購読中止日 / 変更適用日 / 最新データフラグ / 増減報告フラグ / 新規フラグ / 解約フラグ / 引落口座貯金種目 / 引落元口座店舗コード / 引落元口座店舗名 / 引落口座番号 / 引落口座名義）が表示されること
 </t>
           </r>
           <r>
@@ -14648,17 +14648,2067 @@
       <c r="BP49" s="10" t="n"/>
       <c r="BQ49" s="11" t="n"/>
     </row>
+    <row r="50" ht="22.5" customHeight="1">
+      <c r="A50" s="32" t="inlineStr">
+        <is>
+          <t>履歴取消・作成者表示（Function — Torikeshi / Created-by）</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="10" t="n"/>
+      <c r="J50" s="10" t="n"/>
+      <c r="K50" s="10" t="n"/>
+      <c r="L50" s="10" t="n"/>
+      <c r="M50" s="10" t="n"/>
+      <c r="N50" s="10" t="n"/>
+      <c r="O50" s="10" t="n"/>
+      <c r="P50" s="10" t="n"/>
+      <c r="Q50" s="10" t="n"/>
+      <c r="R50" s="10" t="n"/>
+      <c r="S50" s="10" t="n"/>
+      <c r="T50" s="10" t="n"/>
+      <c r="U50" s="10" t="n"/>
+      <c r="V50" s="10" t="n"/>
+      <c r="W50" s="10" t="n"/>
+      <c r="X50" s="10" t="n"/>
+      <c r="Y50" s="10" t="n"/>
+      <c r="Z50" s="10" t="n"/>
+      <c r="AA50" s="10" t="n"/>
+      <c r="AB50" s="10" t="n"/>
+      <c r="AC50" s="10" t="n"/>
+      <c r="AD50" s="10" t="n"/>
+      <c r="AE50" s="10" t="n"/>
+      <c r="AF50" s="10" t="n"/>
+      <c r="AG50" s="10" t="n"/>
+      <c r="AH50" s="10" t="n"/>
+      <c r="AI50" s="10" t="n"/>
+      <c r="AJ50" s="10" t="n"/>
+      <c r="AK50" s="10" t="n"/>
+      <c r="AL50" s="10" t="n"/>
+      <c r="AM50" s="10" t="n"/>
+      <c r="AN50" s="10" t="n"/>
+      <c r="AO50" s="10" t="n"/>
+      <c r="AP50" s="10" t="n"/>
+      <c r="AQ50" s="10" t="n"/>
+      <c r="AR50" s="10" t="n"/>
+      <c r="AS50" s="10" t="n"/>
+      <c r="AT50" s="10" t="n"/>
+      <c r="AU50" s="10" t="n"/>
+      <c r="AV50" s="10" t="n"/>
+      <c r="AW50" s="10" t="n"/>
+      <c r="AX50" s="10" t="n"/>
+      <c r="AY50" s="10" t="n"/>
+      <c r="AZ50" s="10" t="n"/>
+      <c r="BA50" s="10" t="n"/>
+      <c r="BB50" s="10" t="n"/>
+      <c r="BC50" s="10" t="n"/>
+      <c r="BD50" s="10" t="n"/>
+      <c r="BE50" s="10" t="n"/>
+      <c r="BF50" s="10" t="n"/>
+      <c r="BG50" s="10" t="n"/>
+      <c r="BH50" s="10" t="n"/>
+      <c r="BI50" s="10" t="n"/>
+      <c r="BJ50" s="10" t="n"/>
+      <c r="BK50" s="10" t="n"/>
+      <c r="BL50" s="10" t="n"/>
+      <c r="BM50" s="10" t="n"/>
+      <c r="BN50" s="10" t="n"/>
+      <c r="BO50" s="10" t="n"/>
+      <c r="BP50" s="10" t="n"/>
+      <c r="BQ50" s="11" t="n"/>
+    </row>
+    <row r="51" ht="450" customHeight="1">
+      <c r="A51" s="44" t="n">
+        <v>34</v>
+      </c>
+      <c r="B51" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-013-034</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="11" t="n"/>
+      <c r="E51" s="46" t="inlineStr">
+        <is>
+          <t>業務ロジック — 「取消」ボタンの活性条件（顧客要件2026-07）</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="11" t="n"/>
+      <c r="J51" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属、`dokusya.update` 権限あり）
+・紙版（dokusya_shubetsu=1）の購読者に、以下の履歴行が存在すること
+・(a) 新規行（rireki_no=1、shinki_flg=true）
+・(b) 適用日が未来の末尾行（通常変更：増部・住所変更 等）
+・(c) (b) より前の中間行（後続に未取消行あり）
+・(d) 適用日が到来済みの行（適用日 ≤ 本日、JST）
+・(e) 取消済行（torikeshi_flg=true）
+・電子版（dokusya_shubetsu=2）および併読（3）の購読者も各1件存在すること</t>
+        </is>
+      </c>
+      <c r="K51" s="10" t="n"/>
+      <c r="L51" s="10" t="n"/>
+      <c r="M51" s="10" t="n"/>
+      <c r="N51" s="10" t="n"/>
+      <c r="O51" s="10" t="n"/>
+      <c r="P51" s="11" t="n"/>
+      <c r="Q51" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">紙版購読者の購読者履歴情報画面を開き、各行の「取消」ボタンの表示・活性状態を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">API レスポンスの `can_torikeshi` を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">GET /api/v1/dokusya/{dokusya_id}/rireki
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">電子版（dokusya_shubetsu=2）の購読者履歴情報画面を開き、「取消」ボタンの活性状態を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>併読（dokusya_shubetsu=3）の購読者履歴情報画面を開き、「取消」ボタンの活性状態を確認</t>
+          </r>
+        </is>
+      </c>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="10" t="n"/>
+      <c r="T51" s="10" t="n"/>
+      <c r="U51" s="10" t="n"/>
+      <c r="V51" s="10" t="n"/>
+      <c r="W51" s="11" t="n"/>
+      <c r="X51" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「取消」ボタンは全行に**表示**されるが、活性となるのは (b) 適用日が未来の末尾行のみであること。(a) 新規行・(c) 中間行・(d) 適用日到来済み行・(e) 取消済行は**非活性**であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(b) の行のみ `can_torikeshi: true`、他の行はすべて `can_torikeshi: false` であること。(e) の行は `torikeshi_flg: true` であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">全行の「取消」ボタンが非活性であること（電子版は電子版読者管理システムへ即時連携済みのため取消不可）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">全行の「取消」ボタンが非活性であること（併読も電子版連携対象のため）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・取消可能条件は5つすべてを満たす行のみ（画面設計書 §4.2）：紙版／新規でない／取消済でない／適用日が未来（JST）／適用日チェーンの末尾
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・末尾判定は `rireki_no` 最大ではなく、`torikeshi_flg=false` の行のうち（適用日最大・同日 `rireki_no` 最大）で行う。中間レコードは LIFO（末尾から順に）でしか取消できない
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・紙版の解約行は `joho_henko_tekiyo_date = 購読中止日` のため、中止日到来前であれば「解約の取り止め」としてこの条件で取消可能となる</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y51" s="10" t="n"/>
+      <c r="Z51" s="10" t="n"/>
+      <c r="AA51" s="10" t="n"/>
+      <c r="AB51" s="10" t="n"/>
+      <c r="AC51" s="10" t="n"/>
+      <c r="AD51" s="11" t="n"/>
+      <c r="AE51" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF51" s="11" t="n"/>
+      <c r="AG51" s="45" t="inlineStr"/>
+      <c r="AH51" s="10" t="n"/>
+      <c r="AI51" s="11" t="n"/>
+      <c r="AJ51" s="45" t="inlineStr"/>
+      <c r="AK51" s="10" t="n"/>
+      <c r="AL51" s="11" t="n"/>
+      <c r="AM51" s="45" t="inlineStr"/>
+      <c r="AN51" s="10" t="n"/>
+      <c r="AO51" s="11" t="n"/>
+      <c r="AP51" s="45" t="inlineStr"/>
+      <c r="AQ51" s="10" t="n"/>
+      <c r="AR51" s="11" t="n"/>
+      <c r="AS51" s="45" t="inlineStr"/>
+      <c r="AT51" s="10" t="n"/>
+      <c r="AU51" s="11" t="n"/>
+      <c r="AV51" s="45" t="inlineStr"/>
+      <c r="AW51" s="10" t="n"/>
+      <c r="AX51" s="11" t="n"/>
+      <c r="AY51" s="45" t="inlineStr"/>
+      <c r="AZ51" s="10" t="n"/>
+      <c r="BA51" s="11" t="n"/>
+      <c r="BB51" s="45" t="inlineStr"/>
+      <c r="BC51" s="10" t="n"/>
+      <c r="BD51" s="11" t="n"/>
+      <c r="BE51" s="45" t="inlineStr"/>
+      <c r="BF51" s="10" t="n"/>
+      <c r="BG51" s="11" t="n"/>
+      <c r="BH51" s="45" t="inlineStr"/>
+      <c r="BI51" s="10" t="n"/>
+      <c r="BJ51" s="11" t="n"/>
+      <c r="BK51" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL51" s="10" t="n"/>
+      <c r="BM51" s="10" t="n"/>
+      <c r="BN51" s="10" t="n"/>
+      <c r="BO51" s="10" t="n"/>
+      <c r="BP51" s="10" t="n"/>
+      <c r="BQ51" s="11" t="n"/>
+    </row>
+    <row r="52" ht="450" customHeight="1">
+      <c r="A52" s="44" t="n">
+        <v>35</v>
+      </c>
+      <c r="B52" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-013-035</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="46" t="inlineStr">
+        <is>
+          <t>業務ロジック — 履歴取消の正常系（赤伝行の追加とマスタ再計算）</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="11" t="n"/>
+      <c r="J52" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属、`dokusya.update` 権限あり）
+・紙版の購読者に、適用日が未来の末尾行（例：購読部数 1 → 3 への増部）が存在すること
+・取消前の `t_dokusya` の購読部数が 1 であること</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="n"/>
+      <c r="L52" s="10" t="n"/>
+      <c r="M52" s="10" t="n"/>
+      <c r="N52" s="10" t="n"/>
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="11" t="n"/>
+      <c r="Q52" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">対象行の「取消」ボタンを押下し、取消理由に `誤入力のため取消` を入力して実行
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">画面のトースト表示と一覧の再読み込み結果を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DBで対象行と打ち消し行を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT dokusya_rireki_id, rireki_no, joho_henko_tekiyo_date, torikeshi_flg,
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">saishin_data_flg, dokusya_busu, dokusya_busu_zenkai, biko, created_by
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_dokusya_rireki WHERE dokusya_id = :ID ORDER BY rireki_no;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DBで購読者マスタの再計算結果を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT dokusya_busu FROM t_dokusya WHERE dokusya_id = :ID;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>操作ログ（`t_log`）を確認</t>
+          </r>
+        </is>
+      </c>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="10" t="n"/>
+      <c r="T52" s="10" t="n"/>
+      <c r="U52" s="10" t="n"/>
+      <c r="V52" s="10" t="n"/>
+      <c r="W52" s="11" t="n"/>
+      <c r="X52" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード200が返却され、レスポンスが `{"message": "取消しました。"}` であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">トースト `取消しました。` が表示され、一覧が再読み込みされること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">対象行が `torikeshi_flg=true`・`biko='誤入力のため取消'` に更新されていること。さらに次番の `rireki_no` で打ち消し行（赤伝）が1件追加され、以下を満たすこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・現在値と前回値が入れ替わっていること（`dokusya_busu=1`・`dokusya_busu_zenkai=3`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・`joho_henko_tekiyo_date` が対象行と同じであること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・`torikeshi_flg=true`・`saishin_data_flg=false`・`biko='誤入力のため取消'`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・`created_by` が操作者の `m_account.account_id` の文字列であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`t_dokusya.dokusya_busu` が有効な履歴チェーンから再計算され、取消前の値 1 に戻っていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`t_log` に UPDATE が1件記録され、`after_value` に `torikeshi_reason` として取消理由が含まれること。業務更新と同一トランザクションで記録されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・打ち消し行の採番前に `t_dokusya` の対象行をロックし、他の更新との `rireki_no` 競合を防ぐこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・取消理由は対象行・打ち消し行の両方の `biko` と `t_log` の3か所に記録される（顧客要件）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y52" s="10" t="n"/>
+      <c r="Z52" s="10" t="n"/>
+      <c r="AA52" s="10" t="n"/>
+      <c r="AB52" s="10" t="n"/>
+      <c r="AC52" s="10" t="n"/>
+      <c r="AD52" s="11" t="n"/>
+      <c r="AE52" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF52" s="11" t="n"/>
+      <c r="AG52" s="45" t="inlineStr"/>
+      <c r="AH52" s="10" t="n"/>
+      <c r="AI52" s="11" t="n"/>
+      <c r="AJ52" s="45" t="inlineStr"/>
+      <c r="AK52" s="10" t="n"/>
+      <c r="AL52" s="11" t="n"/>
+      <c r="AM52" s="45" t="inlineStr"/>
+      <c r="AN52" s="10" t="n"/>
+      <c r="AO52" s="11" t="n"/>
+      <c r="AP52" s="45" t="inlineStr"/>
+      <c r="AQ52" s="10" t="n"/>
+      <c r="AR52" s="11" t="n"/>
+      <c r="AS52" s="45" t="inlineStr"/>
+      <c r="AT52" s="10" t="n"/>
+      <c r="AU52" s="11" t="n"/>
+      <c r="AV52" s="45" t="inlineStr"/>
+      <c r="AW52" s="10" t="n"/>
+      <c r="AX52" s="11" t="n"/>
+      <c r="AY52" s="45" t="inlineStr"/>
+      <c r="AZ52" s="10" t="n"/>
+      <c r="BA52" s="11" t="n"/>
+      <c r="BB52" s="45" t="inlineStr"/>
+      <c r="BC52" s="10" t="n"/>
+      <c r="BD52" s="11" t="n"/>
+      <c r="BE52" s="45" t="inlineStr"/>
+      <c r="BF52" s="10" t="n"/>
+      <c r="BG52" s="11" t="n"/>
+      <c r="BH52" s="45" t="inlineStr"/>
+      <c r="BI52" s="10" t="n"/>
+      <c r="BJ52" s="11" t="n"/>
+      <c r="BK52" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL52" s="10" t="n"/>
+      <c r="BM52" s="10" t="n"/>
+      <c r="BN52" s="10" t="n"/>
+      <c r="BO52" s="10" t="n"/>
+      <c r="BP52" s="10" t="n"/>
+      <c r="BQ52" s="11" t="n"/>
+    </row>
+    <row r="53" ht="416" customHeight="1">
+      <c r="A53" s="44" t="n">
+        <v>36</v>
+      </c>
+      <c r="B53" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-013-036</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="46" t="inlineStr">
+        <is>
+          <t>入力チェック — 取消理由の必須・最大文字数</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="11" t="n"/>
+      <c r="J53" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属、`dokusya.update` 権限あり）
+・取消可能な履歴行（適用日が未来の紙版末尾行）が存在すること</t>
+        </is>
+      </c>
+      <c r="K53" s="10" t="n"/>
+      <c r="L53" s="10" t="n"/>
+      <c r="M53" s="10" t="n"/>
+      <c r="N53" s="10" t="n"/>
+      <c r="O53" s="10" t="n"/>
+      <c r="P53" s="11" t="n"/>
+      <c r="Q53" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">取消理由を未入力のまま取消を実行
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">取消理由に半角スペースのみを入力して取消を実行
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">取消理由に501文字を入力して取消を実行
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>取消理由に500文字を入力して取消を実行</t>
+          </r>
+        </is>
+      </c>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="10" t="n"/>
+      <c r="T53" s="10" t="n"/>
+      <c r="U53" s="10" t="n"/>
+      <c r="V53" s="10" t="n"/>
+      <c r="W53" s="11" t="n"/>
+      <c r="X53" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード400（`error_code: VALIDATION_ERROR`）が返却され、`errors` に `{"field": "reason", "message": "取消理由を入力してください。"}` が含まれること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1と同じエラーとなること（空白のみは未入力として扱う）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード400（`error_code: VALIDATION_ERROR`）が返却され、`errors` に `{"field": "reason", "message": "取消理由は500文字以内で入力してください。"}` が含まれること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>取消が成功し、`取消しました。` が表示されること（境界値：500文字は許容）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y53" s="10" t="n"/>
+      <c r="Z53" s="10" t="n"/>
+      <c r="AA53" s="10" t="n"/>
+      <c r="AB53" s="10" t="n"/>
+      <c r="AC53" s="10" t="n"/>
+      <c r="AD53" s="11" t="n"/>
+      <c r="AE53" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF53" s="11" t="n"/>
+      <c r="AG53" s="45" t="inlineStr"/>
+      <c r="AH53" s="10" t="n"/>
+      <c r="AI53" s="11" t="n"/>
+      <c r="AJ53" s="45" t="inlineStr"/>
+      <c r="AK53" s="10" t="n"/>
+      <c r="AL53" s="11" t="n"/>
+      <c r="AM53" s="45" t="inlineStr"/>
+      <c r="AN53" s="10" t="n"/>
+      <c r="AO53" s="11" t="n"/>
+      <c r="AP53" s="45" t="inlineStr"/>
+      <c r="AQ53" s="10" t="n"/>
+      <c r="AR53" s="11" t="n"/>
+      <c r="AS53" s="45" t="inlineStr"/>
+      <c r="AT53" s="10" t="n"/>
+      <c r="AU53" s="11" t="n"/>
+      <c r="AV53" s="45" t="inlineStr"/>
+      <c r="AW53" s="10" t="n"/>
+      <c r="AX53" s="11" t="n"/>
+      <c r="AY53" s="45" t="inlineStr"/>
+      <c r="AZ53" s="10" t="n"/>
+      <c r="BA53" s="11" t="n"/>
+      <c r="BB53" s="45" t="inlineStr"/>
+      <c r="BC53" s="10" t="n"/>
+      <c r="BD53" s="11" t="n"/>
+      <c r="BE53" s="45" t="inlineStr"/>
+      <c r="BF53" s="10" t="n"/>
+      <c r="BG53" s="11" t="n"/>
+      <c r="BH53" s="45" t="inlineStr"/>
+      <c r="BI53" s="10" t="n"/>
+      <c r="BJ53" s="11" t="n"/>
+      <c r="BK53" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL53" s="10" t="n"/>
+      <c r="BM53" s="10" t="n"/>
+      <c r="BN53" s="10" t="n"/>
+      <c r="BO53" s="10" t="n"/>
+      <c r="BP53" s="10" t="n"/>
+      <c r="BQ53" s="11" t="n"/>
+    </row>
+    <row r="54" ht="450" customHeight="1">
+      <c r="A54" s="44" t="n">
+        <v>37</v>
+      </c>
+      <c r="B54" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-013-037</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="46" t="inlineStr">
+        <is>
+          <t>業務ロジック — 取消不可レコードへのAPI直接実行（TORIKESHI_NOT_ALLOWED）</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="11" t="n"/>
+      <c r="J54" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属、`dokusya.update` 権限あり）
+・ACSMS-TC-013-034 と同じ (a)〜(e) の履歴行が存在すること
+・画面のボタン非活性を経由せず、API を直接呼び出せること（curl / DevTools）</t>
+        </is>
+      </c>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="10" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="11" t="n"/>
+      <c r="Q54" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(a) 新規行に対して取消APIを直接実行
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">POST /api/v1/dokusya/{dokusya_id}/rireki/{新規行のID}/torikeshi
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">{ "reason": "テスト" }
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(c) 中間行に対して取消APIを直接実行
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(d) 適用日到来済み行に対して取消APIを直接実行
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(e) 取消済行に対して取消APIを直接実行
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">電子版（dokusya_shubetsu=2）の履歴行に対して取消APIを直接実行
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>上記いずれかの実行後、`t_dokusya_rireki` と `t_log` を確認</t>
+          </r>
+        </is>
+      </c>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="10" t="n"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="11" t="n"/>
+      <c r="X54" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1〜5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">いずれも HTTPステータスコード400（`error_code: TORIKESHI_NOT_ALLOWED`）が返却され、メッセージが `取消できないレコードです（紙版・適用日が未来の末尾レコードのみ取消可能。新規・取消済・中間レコード・電子版・適用日到来済みは取消できません）。` であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">履歴行が一切変更されていないこと（`torikeshi_flg` が立たず、打ち消し行も追加されないこと）。また、期待される検証失敗のためエラーログ（`log_type=3`）が記録されていないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・FE のボタン非活性はUXであり、セキュリティ境界ではない。BE は同じ条件でトランザクション開始前に再検証し、さらにトランザクション内の `applyTorikeshi` でも再度ガードする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・トランザクション前に弾くことで、想定内の400をエラーログに残さない（承認/却下APIと同方針）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y54" s="10" t="n"/>
+      <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
+      <c r="AB54" s="10" t="n"/>
+      <c r="AC54" s="10" t="n"/>
+      <c r="AD54" s="11" t="n"/>
+      <c r="AE54" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF54" s="11" t="n"/>
+      <c r="AG54" s="45" t="inlineStr"/>
+      <c r="AH54" s="10" t="n"/>
+      <c r="AI54" s="11" t="n"/>
+      <c r="AJ54" s="45" t="inlineStr"/>
+      <c r="AK54" s="10" t="n"/>
+      <c r="AL54" s="11" t="n"/>
+      <c r="AM54" s="45" t="inlineStr"/>
+      <c r="AN54" s="10" t="n"/>
+      <c r="AO54" s="11" t="n"/>
+      <c r="AP54" s="45" t="inlineStr"/>
+      <c r="AQ54" s="10" t="n"/>
+      <c r="AR54" s="11" t="n"/>
+      <c r="AS54" s="45" t="inlineStr"/>
+      <c r="AT54" s="10" t="n"/>
+      <c r="AU54" s="11" t="n"/>
+      <c r="AV54" s="45" t="inlineStr"/>
+      <c r="AW54" s="10" t="n"/>
+      <c r="AX54" s="11" t="n"/>
+      <c r="AY54" s="45" t="inlineStr"/>
+      <c r="AZ54" s="10" t="n"/>
+      <c r="BA54" s="11" t="n"/>
+      <c r="BB54" s="45" t="inlineStr"/>
+      <c r="BC54" s="10" t="n"/>
+      <c r="BD54" s="11" t="n"/>
+      <c r="BE54" s="45" t="inlineStr"/>
+      <c r="BF54" s="10" t="n"/>
+      <c r="BG54" s="11" t="n"/>
+      <c r="BH54" s="45" t="inlineStr"/>
+      <c r="BI54" s="10" t="n"/>
+      <c r="BJ54" s="11" t="n"/>
+      <c r="BK54" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL54" s="10" t="n"/>
+      <c r="BM54" s="10" t="n"/>
+      <c r="BN54" s="10" t="n"/>
+      <c r="BO54" s="10" t="n"/>
+      <c r="BP54" s="10" t="n"/>
+      <c r="BQ54" s="11" t="n"/>
+    </row>
+    <row r="55" ht="450" customHeight="1">
+      <c r="A55" s="44" t="n">
+        <v>38</v>
+      </c>
+      <c r="B55" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-013-038</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="11" t="n"/>
+      <c r="E55" s="46" t="inlineStr">
+        <is>
+          <t>アクセス権限制御 — 取消APIのデータスコープと履歴IDの帰属チェック</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="11" t="n"/>
+      <c r="J55" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属、`dokusya.update` 権限あり）
+・自JA（ja_id=100）に取消可能な履歴行を持つ購読者Aが存在すること
+・別JA（ja_id=200）に取消可能な履歴行を持つ購読者Bが存在すること</t>
+        </is>
+      </c>
+      <c r="K55" s="10" t="n"/>
+      <c r="L55" s="10" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="10" t="n"/>
+      <c r="O55" s="10" t="n"/>
+      <c r="P55" s="11" t="n"/>
+      <c r="Q55" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読者A（自JA）のIDに対し、**購読者Bの履歴ID**を指定して取消APIを実行
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読者B（別JA）のIDと購読者Bの履歴IDを指定して取消APIを実行
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">存在しない履歴ID（例：99999999）を指定して取消APIを実行
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>`dokusya.update` 権限を持たないロール（例：閲覧のみのアカウント）で取消APIを実行</t>
+          </r>
+        </is>
+      </c>
+      <c r="R55" s="10" t="n"/>
+      <c r="S55" s="10" t="n"/>
+      <c r="T55" s="10" t="n"/>
+      <c r="U55" s="10" t="n"/>
+      <c r="V55" s="10" t="n"/>
+      <c r="W55" s="11" t="n"/>
+      <c r="X55" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード404（`error_code: NOT_FOUND`）が返却されること。履歴は `dokusya_rireki_id` と `dokusya_id` の AND で取得するため、他購読者の履歴IDを与えても取消されないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード404（`error_code: NOT_FOUND`）が返却されること。DataScope 範囲外は行の存在を秘匿するため 403 ではなく **404 でマスク**されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード404（`error_code: NOT_FOUND`）が返却されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード403（`error_code: FORBIDDEN`、メッセージ `この画面へのアクセス権限がありません。`）が返却されること。画面上も全行の「取消」ボタンが非活性であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・ステップ1は履歴IDの総当たりによる他購読者データの改変を防ぐためのチェック
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・ステップ2の404マスクは Layer 2 DataScope の方針（`security.md`）に準拠</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y55" s="10" t="n"/>
+      <c r="Z55" s="10" t="n"/>
+      <c r="AA55" s="10" t="n"/>
+      <c r="AB55" s="10" t="n"/>
+      <c r="AC55" s="10" t="n"/>
+      <c r="AD55" s="11" t="n"/>
+      <c r="AE55" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF55" s="11" t="n"/>
+      <c r="AG55" s="45" t="inlineStr"/>
+      <c r="AH55" s="10" t="n"/>
+      <c r="AI55" s="11" t="n"/>
+      <c r="AJ55" s="45" t="inlineStr"/>
+      <c r="AK55" s="10" t="n"/>
+      <c r="AL55" s="11" t="n"/>
+      <c r="AM55" s="45" t="inlineStr"/>
+      <c r="AN55" s="10" t="n"/>
+      <c r="AO55" s="11" t="n"/>
+      <c r="AP55" s="45" t="inlineStr"/>
+      <c r="AQ55" s="10" t="n"/>
+      <c r="AR55" s="11" t="n"/>
+      <c r="AS55" s="45" t="inlineStr"/>
+      <c r="AT55" s="10" t="n"/>
+      <c r="AU55" s="11" t="n"/>
+      <c r="AV55" s="45" t="inlineStr"/>
+      <c r="AW55" s="10" t="n"/>
+      <c r="AX55" s="11" t="n"/>
+      <c r="AY55" s="45" t="inlineStr"/>
+      <c r="AZ55" s="10" t="n"/>
+      <c r="BA55" s="11" t="n"/>
+      <c r="BB55" s="45" t="inlineStr"/>
+      <c r="BC55" s="10" t="n"/>
+      <c r="BD55" s="11" t="n"/>
+      <c r="BE55" s="45" t="inlineStr"/>
+      <c r="BF55" s="10" t="n"/>
+      <c r="BG55" s="11" t="n"/>
+      <c r="BH55" s="45" t="inlineStr"/>
+      <c r="BI55" s="10" t="n"/>
+      <c r="BJ55" s="11" t="n"/>
+      <c r="BK55" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL55" s="10" t="n"/>
+      <c r="BM55" s="10" t="n"/>
+      <c r="BN55" s="10" t="n"/>
+      <c r="BO55" s="10" t="n"/>
+      <c r="BP55" s="10" t="n"/>
+      <c r="BQ55" s="11" t="n"/>
+    </row>
+    <row r="56" ht="416" customHeight="1">
+      <c r="A56" s="44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B56" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-013-039</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="46" t="inlineStr">
+        <is>
+          <t>画面表示 — 取消済行の表示（打ち消し線）と赤伝行の並び</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="11" t="n"/>
+      <c r="J56" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・ACSMS-TC-013-035 を実行済みで、取消済行と打ち消し行（赤伝）が存在すること</t>
+        </is>
+      </c>
+      <c r="K56" s="10" t="n"/>
+      <c r="L56" s="10" t="n"/>
+      <c r="M56" s="10" t="n"/>
+      <c r="N56" s="10" t="n"/>
+      <c r="O56" s="10" t="n"/>
+      <c r="P56" s="11" t="n"/>
+      <c r="Q56" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読者履歴情報画面を開き、取消済行の表示スタイルを確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">打ち消し行（赤伝）の表示位置と内容を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>一覧のソート順（履歴番号の降順）を確認</t>
+          </r>
+        </is>
+      </c>
+      <c r="R56" s="10" t="n"/>
+      <c r="S56" s="10" t="n"/>
+      <c r="T56" s="10" t="n"/>
+      <c r="U56" s="10" t="n"/>
+      <c r="V56" s="10" t="n"/>
+      <c r="W56" s="11" t="n"/>
+      <c r="X56" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`torikeshi_flg=true` の行が打ち消し線付きで表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">打ち消し行が最新（履歴番号が最大）として先頭に表示され、値が取消対象行の前回値に戻っていること。打ち消し行自体も `torikeshi_flg=true` のため打ち消し線付きで表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">既定の並び順が履歴番号の降順であること（最新履歴が先頭）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・打ち消し行は対象行と同じ適用日を持つため、適用日でソートした場合は隣接して並ぶ
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・取消済の2行（対象行・打ち消し行）は以後の取消対象にならない（`can_torikeshi=false`）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y56" s="10" t="n"/>
+      <c r="Z56" s="10" t="n"/>
+      <c r="AA56" s="10" t="n"/>
+      <c r="AB56" s="10" t="n"/>
+      <c r="AC56" s="10" t="n"/>
+      <c r="AD56" s="11" t="n"/>
+      <c r="AE56" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF56" s="11" t="n"/>
+      <c r="AG56" s="45" t="inlineStr"/>
+      <c r="AH56" s="10" t="n"/>
+      <c r="AI56" s="11" t="n"/>
+      <c r="AJ56" s="45" t="inlineStr"/>
+      <c r="AK56" s="10" t="n"/>
+      <c r="AL56" s="11" t="n"/>
+      <c r="AM56" s="45" t="inlineStr"/>
+      <c r="AN56" s="10" t="n"/>
+      <c r="AO56" s="11" t="n"/>
+      <c r="AP56" s="45" t="inlineStr"/>
+      <c r="AQ56" s="10" t="n"/>
+      <c r="AR56" s="11" t="n"/>
+      <c r="AS56" s="45" t="inlineStr"/>
+      <c r="AT56" s="10" t="n"/>
+      <c r="AU56" s="11" t="n"/>
+      <c r="AV56" s="45" t="inlineStr"/>
+      <c r="AW56" s="10" t="n"/>
+      <c r="AX56" s="11" t="n"/>
+      <c r="AY56" s="45" t="inlineStr"/>
+      <c r="AZ56" s="10" t="n"/>
+      <c r="BA56" s="11" t="n"/>
+      <c r="BB56" s="45" t="inlineStr"/>
+      <c r="BC56" s="10" t="n"/>
+      <c r="BD56" s="11" t="n"/>
+      <c r="BE56" s="45" t="inlineStr"/>
+      <c r="BF56" s="10" t="n"/>
+      <c r="BG56" s="11" t="n"/>
+      <c r="BH56" s="45" t="inlineStr"/>
+      <c r="BI56" s="10" t="n"/>
+      <c r="BJ56" s="11" t="n"/>
+      <c r="BK56" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL56" s="10" t="n"/>
+      <c r="BM56" s="10" t="n"/>
+      <c r="BN56" s="10" t="n"/>
+      <c r="BO56" s="10" t="n"/>
+      <c r="BP56" s="10" t="n"/>
+      <c r="BQ56" s="11" t="n"/>
+    </row>
+    <row r="57" ht="368" customHeight="1">
+      <c r="A57" s="44" t="n">
+        <v>40</v>
+      </c>
+      <c r="B57" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-013-040</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="46" t="inlineStr">
+        <is>
+          <t>画面表示 — 作成者（created_by）の表示内容（#55719）</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="11" t="n"/>
+      <c r="J57" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・画面操作で作成された履歴行が存在すること
+・読者同期バッチ（電子版連携）で作成された履歴行が存在すること</t>
+        </is>
+      </c>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="11" t="n"/>
+      <c r="Q57" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">画面操作で作成された履歴行の `created_by` を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">GET /api/v1/dokusya/{dokusya_id}/rireki
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">読者同期バッチで作成された履歴行の `created_by` を確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT DISTINCT created_by FROM t_dokusya_rireki WHERE dokusya_id = :ID;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>画面上の該当列の表示を確認</t>
+          </r>
+        </is>
+      </c>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="11" t="n"/>
+      <c r="X57" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`created_by` が操作者の `m_account.account_id` の文字列（例 `"539"`）であること。ログインID（例 `ja_honten01`）ではないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">バッチ作成行は `SYSTEM_DENSHI_SYNC` 等の `SYSTEM_*` 固定名であること（#55719 でバッチ実行者名を `SYSTEM_*` に統一）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">値がそのまま表示され、レイアウト崩れが起きないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・API設計書 v1.4 の記載是正に対応する確認（実装は以前から account_id 文字列 / SYSTEM_* を格納していた）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y57" s="10" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="10" t="n"/>
+      <c r="AD57" s="11" t="n"/>
+      <c r="AE57" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF57" s="11" t="n"/>
+      <c r="AG57" s="45" t="inlineStr"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="11" t="n"/>
+      <c r="AJ57" s="45" t="inlineStr"/>
+      <c r="AK57" s="10" t="n"/>
+      <c r="AL57" s="11" t="n"/>
+      <c r="AM57" s="45" t="inlineStr"/>
+      <c r="AN57" s="10" t="n"/>
+      <c r="AO57" s="11" t="n"/>
+      <c r="AP57" s="45" t="inlineStr"/>
+      <c r="AQ57" s="10" t="n"/>
+      <c r="AR57" s="11" t="n"/>
+      <c r="AS57" s="45" t="inlineStr"/>
+      <c r="AT57" s="10" t="n"/>
+      <c r="AU57" s="11" t="n"/>
+      <c r="AV57" s="45" t="inlineStr"/>
+      <c r="AW57" s="10" t="n"/>
+      <c r="AX57" s="11" t="n"/>
+      <c r="AY57" s="45" t="inlineStr"/>
+      <c r="AZ57" s="10" t="n"/>
+      <c r="BA57" s="11" t="n"/>
+      <c r="BB57" s="45" t="inlineStr"/>
+      <c r="BC57" s="10" t="n"/>
+      <c r="BD57" s="11" t="n"/>
+      <c r="BE57" s="45" t="inlineStr"/>
+      <c r="BF57" s="10" t="n"/>
+      <c r="BG57" s="11" t="n"/>
+      <c r="BH57" s="45" t="inlineStr"/>
+      <c r="BI57" s="10" t="n"/>
+      <c r="BJ57" s="11" t="n"/>
+      <c r="BK57" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL57" s="10" t="n"/>
+      <c r="BM57" s="10" t="n"/>
+      <c r="BN57" s="10" t="n"/>
+      <c r="BO57" s="10" t="n"/>
+      <c r="BP57" s="10" t="n"/>
+      <c r="BQ57" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="632">
+  <mergeCells count="752">
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="AS46:AU46"/>
+    <mergeCell ref="AE54:AF54"/>
     <mergeCell ref="BH33:BJ33"/>
+    <mergeCell ref="E52:I52"/>
     <mergeCell ref="AE41:AF41"/>
+    <mergeCell ref="AV57:AX57"/>
+    <mergeCell ref="B53:D53"/>
     <mergeCell ref="E39:I39"/>
     <mergeCell ref="E14:I14"/>
     <mergeCell ref="W7:Y7"/>
     <mergeCell ref="AS48:AU48"/>
     <mergeCell ref="BK16:BQ16"/>
+    <mergeCell ref="AE56:AF56"/>
     <mergeCell ref="AE43:AF43"/>
     <mergeCell ref="AM30:AO30"/>
     <mergeCell ref="AP45:AR45"/>
@@ -14668,6 +16718,7 @@
     <mergeCell ref="AM21:AO21"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="BH39:BJ39"/>
+    <mergeCell ref="J57:P57"/>
     <mergeCell ref="W2:AH2"/>
     <mergeCell ref="X10:AD11"/>
     <mergeCell ref="AJ22:AL22"/>
@@ -14675,10 +16726,12 @@
     <mergeCell ref="AP13:AR13"/>
     <mergeCell ref="Q38:W38"/>
     <mergeCell ref="AE34:AF34"/>
+    <mergeCell ref="AJ51:AL51"/>
     <mergeCell ref="BK47:BQ47"/>
     <mergeCell ref="E25:I25"/>
     <mergeCell ref="Q40:W40"/>
     <mergeCell ref="AE36:AF36"/>
+    <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
     <mergeCell ref="AV39:AX39"/>
     <mergeCell ref="BH21:BJ21"/>
@@ -14686,6 +16739,7 @@
     <mergeCell ref="AJ38:AL38"/>
     <mergeCell ref="BK48:BQ48"/>
     <mergeCell ref="AM49:AO49"/>
+    <mergeCell ref="AG52:AI52"/>
     <mergeCell ref="BE22:BG22"/>
     <mergeCell ref="BH23:BJ23"/>
     <mergeCell ref="BB26:BD26"/>
@@ -14701,13 +16755,17 @@
     <mergeCell ref="AF8:AH8"/>
     <mergeCell ref="AY31:BA31"/>
     <mergeCell ref="BK37:BQ37"/>
+    <mergeCell ref="AM55:AO55"/>
     <mergeCell ref="BH34:BJ34"/>
     <mergeCell ref="X23:AD23"/>
     <mergeCell ref="BE38:BG38"/>
     <mergeCell ref="BH49:BJ49"/>
     <mergeCell ref="R3:V3"/>
+    <mergeCell ref="AP53:AR53"/>
     <mergeCell ref="X16:AD16"/>
     <mergeCell ref="AP28:AR28"/>
+    <mergeCell ref="AE57:AF57"/>
+    <mergeCell ref="BK53:BQ53"/>
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
@@ -14716,9 +16774,11 @@
     <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="BK13:BQ13"/>
     <mergeCell ref="B21:D21"/>
+    <mergeCell ref="AY57:BA57"/>
     <mergeCell ref="BE41:BG41"/>
     <mergeCell ref="J25:P25"/>
     <mergeCell ref="Q46:W46"/>
+    <mergeCell ref="BH55:BJ55"/>
     <mergeCell ref="AM24:AO24"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="BB38:BD38"/>
@@ -14733,11 +16793,16 @@
     <mergeCell ref="BH29:BJ29"/>
     <mergeCell ref="Q41:W41"/>
     <mergeCell ref="AY44:BA44"/>
+    <mergeCell ref="AV53:AX53"/>
     <mergeCell ref="BH44:BJ44"/>
     <mergeCell ref="AS19:AU19"/>
+    <mergeCell ref="Q56:W56"/>
+    <mergeCell ref="AE52:AF52"/>
     <mergeCell ref="Q43:W43"/>
     <mergeCell ref="J14:P14"/>
     <mergeCell ref="AE39:AF39"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="AJ54:AL54"/>
     <mergeCell ref="AM15:AO15"/>
     <mergeCell ref="AP16:AR16"/>
     <mergeCell ref="BH24:BJ24"/>
@@ -14747,14 +16812,19 @@
     <mergeCell ref="AJ41:AL41"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="BK10:BQ11"/>
+    <mergeCell ref="J53:P53"/>
     <mergeCell ref="AS14:AU14"/>
+    <mergeCell ref="AE53:AF53"/>
+    <mergeCell ref="AG55:AI55"/>
     <mergeCell ref="AP18:AR18"/>
+    <mergeCell ref="AJ56:AL56"/>
     <mergeCell ref="BH26:BJ26"/>
     <mergeCell ref="AG38:AI38"/>
     <mergeCell ref="BE30:BG30"/>
     <mergeCell ref="AJ43:AL43"/>
     <mergeCell ref="AV25:AX25"/>
     <mergeCell ref="W6:Y6"/>
+    <mergeCell ref="J55:P55"/>
     <mergeCell ref="BE29:BG29"/>
     <mergeCell ref="BK28:BQ28"/>
     <mergeCell ref="AY32:BA32"/>
@@ -14767,6 +16837,7 @@
     <mergeCell ref="AY47:BA47"/>
     <mergeCell ref="E21:I21"/>
     <mergeCell ref="Q36:W36"/>
+    <mergeCell ref="BE54:BG54"/>
     <mergeCell ref="Q30:W30"/>
     <mergeCell ref="X26:AD26"/>
     <mergeCell ref="W1:AH1"/>
@@ -14774,9 +16845,11 @@
     <mergeCell ref="AP44:AR44"/>
     <mergeCell ref="E23:I23"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="BE56:BG56"/>
     <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
     <mergeCell ref="BB46:BD46"/>
+    <mergeCell ref="BE57:BG57"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
@@ -14790,6 +16863,7 @@
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="AY45:BA45"/>
     <mergeCell ref="E36:I36"/>
+    <mergeCell ref="Q51:W51"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="BH45:BJ45"/>
     <mergeCell ref="AP24:AR24"/>
@@ -14800,11 +16874,13 @@
     <mergeCell ref="AS22:AU22"/>
     <mergeCell ref="AP26:AR26"/>
     <mergeCell ref="X14:AD14"/>
+    <mergeCell ref="AE55:AF55"/>
     <mergeCell ref="AG21:AI21"/>
     <mergeCell ref="X38:AD38"/>
     <mergeCell ref="BH46:BJ46"/>
     <mergeCell ref="BE44:BG44"/>
     <mergeCell ref="AP19:AR19"/>
+    <mergeCell ref="AJ57:AL57"/>
     <mergeCell ref="BE31:BG31"/>
     <mergeCell ref="J21:P21"/>
     <mergeCell ref="A1:E1"/>
@@ -14827,6 +16903,7 @@
     <mergeCell ref="AV36:AX36"/>
     <mergeCell ref="T6:V6"/>
     <mergeCell ref="AV30:AX30"/>
+    <mergeCell ref="Q52:W52"/>
     <mergeCell ref="Q39:W39"/>
     <mergeCell ref="AS33:AU33"/>
     <mergeCell ref="AM36:AO36"/>
@@ -14840,12 +16917,16 @@
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
     <mergeCell ref="AV21:AX21"/>
+    <mergeCell ref="AY53:BA53"/>
     <mergeCell ref="BK24:BQ24"/>
     <mergeCell ref="X45:AD45"/>
     <mergeCell ref="AG11:AI11"/>
+    <mergeCell ref="BH53:BJ53"/>
     <mergeCell ref="AV29:AX29"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="AV23:AX23"/>
+    <mergeCell ref="BB51:BD51"/>
+    <mergeCell ref="AY55:BA55"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
     <mergeCell ref="BK19:BQ19"/>
@@ -14867,29 +16948,39 @@
     <mergeCell ref="BB11:BD11"/>
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="B45:D45"/>
+    <mergeCell ref="BE53:BG53"/>
     <mergeCell ref="AM32:AO32"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="AM26:AO26"/>
     <mergeCell ref="J24:P24"/>
+    <mergeCell ref="AG51:AI51"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="Q14:W14"/>
+    <mergeCell ref="E57:I57"/>
     <mergeCell ref="B46:D46"/>
+    <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="J26:P26"/>
     <mergeCell ref="AS41:AU41"/>
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="AV55:AX55"/>
     <mergeCell ref="E47:I47"/>
     <mergeCell ref="BB39:BD39"/>
     <mergeCell ref="B48:D48"/>
+    <mergeCell ref="AV52:AX52"/>
+    <mergeCell ref="AP55:AR55"/>
+    <mergeCell ref="AS56:AU56"/>
     <mergeCell ref="AP38:AR38"/>
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
     <mergeCell ref="BE25:BG25"/>
     <mergeCell ref="BK38:BQ38"/>
     <mergeCell ref="F4:AH4"/>
+    <mergeCell ref="X51:AD51"/>
     <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="AM52:AO52"/>
     <mergeCell ref="AG17:AI17"/>
     <mergeCell ref="AS36:AU36"/>
     <mergeCell ref="AM39:AO39"/>
@@ -14898,6 +16989,7 @@
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="AG19:AI19"/>
     <mergeCell ref="X36:AD36"/>
+    <mergeCell ref="J52:P52"/>
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
@@ -14919,6 +17011,7 @@
     <mergeCell ref="AM23:AO23"/>
     <mergeCell ref="AE24:AF24"/>
     <mergeCell ref="AS44:AU44"/>
+    <mergeCell ref="BE55:BG55"/>
     <mergeCell ref="AS31:AU31"/>
     <mergeCell ref="BH18:BJ18"/>
     <mergeCell ref="J32:P32"/>
@@ -14930,11 +17023,13 @@
     <mergeCell ref="AY24:BA24"/>
     <mergeCell ref="AJ28:AL28"/>
     <mergeCell ref="BK17:BQ17"/>
+    <mergeCell ref="BK55:BQ55"/>
     <mergeCell ref="AP30:AR30"/>
     <mergeCell ref="AJ30:AL30"/>
     <mergeCell ref="AP46:AR46"/>
     <mergeCell ref="BK46:BQ46"/>
     <mergeCell ref="BK40:BQ40"/>
+    <mergeCell ref="AS57:AU57"/>
     <mergeCell ref="AY19:BA19"/>
     <mergeCell ref="BK25:BQ25"/>
     <mergeCell ref="Q21:W21"/>
@@ -14942,14 +17037,17 @@
     <mergeCell ref="AP48:AR48"/>
     <mergeCell ref="A27:BQ27"/>
     <mergeCell ref="AE44:AF44"/>
+    <mergeCell ref="X57:AD57"/>
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="AP41:AR41"/>
     <mergeCell ref="AM18:AO18"/>
     <mergeCell ref="BK41:BQ41"/>
     <mergeCell ref="BB13:BD13"/>
     <mergeCell ref="AM17:AO17"/>
+    <mergeCell ref="AP56:AR56"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="AP43:AR43"/>
+    <mergeCell ref="AM53:AO53"/>
     <mergeCell ref="AM47:AO47"/>
     <mergeCell ref="B10:D11"/>
     <mergeCell ref="J45:P45"/>
@@ -14958,15 +17056,19 @@
     <mergeCell ref="AG22:AI22"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="E53:I53"/>
     <mergeCell ref="AM48:AO48"/>
     <mergeCell ref="Q49:W49"/>
     <mergeCell ref="BK43:BQ43"/>
     <mergeCell ref="AM44:AO44"/>
+    <mergeCell ref="B57:D57"/>
     <mergeCell ref="AF6:AH6"/>
+    <mergeCell ref="E55:I55"/>
     <mergeCell ref="AE32:AF32"/>
     <mergeCell ref="AV48:AX48"/>
     <mergeCell ref="AY14:BA14"/>
     <mergeCell ref="AJ18:AL18"/>
+    <mergeCell ref="J51:P51"/>
     <mergeCell ref="F2:Q2"/>
     <mergeCell ref="AS39:AU39"/>
     <mergeCell ref="BH17:BJ17"/>
@@ -14987,13 +17089,16 @@
     <mergeCell ref="BK30:BQ30"/>
     <mergeCell ref="BK36:BQ36"/>
     <mergeCell ref="AS47:AU47"/>
+    <mergeCell ref="AY54:BA54"/>
     <mergeCell ref="AJ29:AL29"/>
     <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="X17:AD17"/>
     <mergeCell ref="AJ44:AL44"/>
+    <mergeCell ref="Q54:W54"/>
     <mergeCell ref="BE18:BG18"/>
     <mergeCell ref="AJ31:AL31"/>
     <mergeCell ref="Q29:W29"/>
+    <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="X19:AD19"/>
     <mergeCell ref="AG34:AI34"/>
@@ -15002,21 +17107,27 @@
     <mergeCell ref="Q31:W31"/>
     <mergeCell ref="BE49:BG49"/>
     <mergeCell ref="E10:I11"/>
+    <mergeCell ref="BK56:BQ56"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="BH37:BJ37"/>
     <mergeCell ref="AE45:AF45"/>
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="R1:V1"/>
+    <mergeCell ref="AP51:AR51"/>
+    <mergeCell ref="BK51:BQ51"/>
     <mergeCell ref="B17:D17"/>
+    <mergeCell ref="BB54:BD54"/>
     <mergeCell ref="AE22:AF22"/>
     <mergeCell ref="BB41:BD41"/>
     <mergeCell ref="J46:P46"/>
     <mergeCell ref="AE46:AF46"/>
+    <mergeCell ref="BH51:BJ51"/>
     <mergeCell ref="Z8:AB8"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="AY11:BA11"/>
+    <mergeCell ref="Q57:W57"/>
     <mergeCell ref="J48:P48"/>
     <mergeCell ref="AJ26:AL26"/>
     <mergeCell ref="AS13:AU13"/>
@@ -15024,12 +17135,15 @@
     <mergeCell ref="AY40:BA40"/>
     <mergeCell ref="A12:BQ12"/>
     <mergeCell ref="AY15:BA15"/>
+    <mergeCell ref="AS53:AU53"/>
     <mergeCell ref="AG23:AI23"/>
     <mergeCell ref="BH40:BJ40"/>
     <mergeCell ref="X13:AD13"/>
     <mergeCell ref="AS15:AU15"/>
     <mergeCell ref="AE48:AF48"/>
+    <mergeCell ref="AS55:AU55"/>
     <mergeCell ref="BE37:BG37"/>
+    <mergeCell ref="AG54:AI54"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="BE24:BG24"/>
     <mergeCell ref="BH25:BJ25"/>
@@ -15038,7 +17152,10 @@
     <mergeCell ref="AG41:AI41"/>
     <mergeCell ref="AP39:AR39"/>
     <mergeCell ref="AP14:AR14"/>
+    <mergeCell ref="AJ52:AL52"/>
     <mergeCell ref="BH22:BJ22"/>
+    <mergeCell ref="BK52:BQ52"/>
+    <mergeCell ref="AG56:AI56"/>
     <mergeCell ref="BE26:BG26"/>
     <mergeCell ref="J16:P16"/>
     <mergeCell ref="AJ39:AL39"/>
@@ -15050,6 +17167,7 @@
     <mergeCell ref="AS25:AU25"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="AG49:AI49"/>
+    <mergeCell ref="AE51:AF51"/>
     <mergeCell ref="BB29:BD29"/>
     <mergeCell ref="BB23:BD23"/>
     <mergeCell ref="E24:I24"/>
@@ -15064,7 +17182,9 @@
     <mergeCell ref="Q47:W47"/>
     <mergeCell ref="BH13:BJ13"/>
     <mergeCell ref="E19:I19"/>
+    <mergeCell ref="BE52:BG52"/>
     <mergeCell ref="BK21:BQ21"/>
+    <mergeCell ref="BB56:BD56"/>
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
@@ -15072,6 +17192,7 @@
     <mergeCell ref="AP25:AR25"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="AY46:BA46"/>
+    <mergeCell ref="BB57:BD57"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="AV16:AX16"/>
     <mergeCell ref="AJ40:AL40"/>
@@ -15083,6 +17204,7 @@
     <mergeCell ref="E37:I37"/>
     <mergeCell ref="X33:AD33"/>
     <mergeCell ref="AV17:AX17"/>
+    <mergeCell ref="AY56:BA56"/>
     <mergeCell ref="AV11:AX11"/>
     <mergeCell ref="AS21:AU21"/>
     <mergeCell ref="AY43:BA43"/>
@@ -15101,13 +17223,18 @@
     <mergeCell ref="AP15:AR15"/>
     <mergeCell ref="AS16:AU16"/>
     <mergeCell ref="BB44:BD44"/>
+    <mergeCell ref="AJ53:AL53"/>
     <mergeCell ref="AV10:BJ10"/>
     <mergeCell ref="BH28:BJ28"/>
     <mergeCell ref="J17:P17"/>
+    <mergeCell ref="AM54:AO54"/>
     <mergeCell ref="AV44:AX44"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="AJ45:AL45"/>
+    <mergeCell ref="AG57:AI57"/>
     <mergeCell ref="B15:D15"/>
+    <mergeCell ref="BB52:BD52"/>
+    <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="AY34:BA34"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="J19:P19"/>
@@ -15115,6 +17242,7 @@
     <mergeCell ref="AS34:AU34"/>
     <mergeCell ref="BB45:BD45"/>
     <mergeCell ref="BB32:BD32"/>
+    <mergeCell ref="Q55:W55"/>
     <mergeCell ref="AY36:BA36"/>
     <mergeCell ref="AS49:AU49"/>
     <mergeCell ref="X34:AD34"/>
@@ -15123,21 +17251,27 @@
     <mergeCell ref="BB47:BD47"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="A35:BQ35"/>
+    <mergeCell ref="BH54:BJ54"/>
     <mergeCell ref="AP33:AR33"/>
     <mergeCell ref="BH41:BJ41"/>
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
     <mergeCell ref="E22:I22"/>
+    <mergeCell ref="BH56:BJ56"/>
     <mergeCell ref="X29:AD29"/>
     <mergeCell ref="BH31:BJ31"/>
     <mergeCell ref="AJ48:AL48"/>
     <mergeCell ref="BE46:BG46"/>
+    <mergeCell ref="X54:AD54"/>
     <mergeCell ref="AY28:BA28"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="AV19:AX19"/>
     <mergeCell ref="AS23:AU23"/>
     <mergeCell ref="E38:I38"/>
+    <mergeCell ref="AY51:BA51"/>
+    <mergeCell ref="Q53:W53"/>
+    <mergeCell ref="X56:AD56"/>
     <mergeCell ref="BK22:BQ22"/>
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="X43:AD43"/>
@@ -15155,21 +17289,29 @@
     <mergeCell ref="Z6:AB6"/>
     <mergeCell ref="AP21:AR21"/>
     <mergeCell ref="AS26:AU26"/>
+    <mergeCell ref="B54:D54"/>
     <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="AJ21:AL21"/>
     <mergeCell ref="AG25:AI25"/>
     <mergeCell ref="AY33:BA33"/>
+    <mergeCell ref="BB53:BD53"/>
     <mergeCell ref="T5:AH5"/>
     <mergeCell ref="AM22:AO22"/>
     <mergeCell ref="AP23:AR23"/>
+    <mergeCell ref="B56:D56"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="B43:D43"/>
+    <mergeCell ref="BE51:BG51"/>
+    <mergeCell ref="BB55:BD55"/>
     <mergeCell ref="BK33:BQ33"/>
     <mergeCell ref="A5:S5"/>
     <mergeCell ref="J22:P22"/>
     <mergeCell ref="AV38:AX38"/>
+    <mergeCell ref="AY52:BA52"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="AY39:BA39"/>
+    <mergeCell ref="AS52:AU52"/>
+    <mergeCell ref="AG53:AI53"/>
     <mergeCell ref="X44:AD44"/>
     <mergeCell ref="AP34:AR34"/>
     <mergeCell ref="AM11:AO11"/>
@@ -15178,6 +17320,7 @@
     <mergeCell ref="BB25:BD25"/>
     <mergeCell ref="AP49:AR49"/>
     <mergeCell ref="E28:I28"/>
+    <mergeCell ref="BH57:BJ57"/>
     <mergeCell ref="AG13:AI13"/>
     <mergeCell ref="AV33:AX33"/>
     <mergeCell ref="AP36:AR36"/>
@@ -15202,12 +17345,16 @@
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="X49:AD49"/>
+    <mergeCell ref="E54:I54"/>
     <mergeCell ref="AV22:AX22"/>
     <mergeCell ref="AY23:BA23"/>
     <mergeCell ref="E41:I41"/>
+    <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="F3:Q3"/>
+    <mergeCell ref="E56:I56"/>
     <mergeCell ref="AP29:AR29"/>
+    <mergeCell ref="AV51:AX51"/>
     <mergeCell ref="E43:I43"/>
     <mergeCell ref="BB15:BD15"/>
     <mergeCell ref="BE16:BG16"/>
@@ -15215,8 +17362,10 @@
     <mergeCell ref="BK23:BQ23"/>
     <mergeCell ref="AE25:AF25"/>
     <mergeCell ref="AS40:AU40"/>
+    <mergeCell ref="BH52:BJ52"/>
     <mergeCell ref="AP31:AR31"/>
     <mergeCell ref="BH14:BJ14"/>
+    <mergeCell ref="BK54:BQ54"/>
     <mergeCell ref="AJ37:AL37"/>
     <mergeCell ref="AY49:BA49"/>
     <mergeCell ref="BE11:BG11"/>
@@ -15226,18 +17375,24 @@
     <mergeCell ref="AV40:AX40"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="J28:P28"/>
+    <mergeCell ref="X52:AD52"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="Q18:W18"/>
     <mergeCell ref="BK49:BQ49"/>
+    <mergeCell ref="A50:BQ50"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE38:AF38"/>
+    <mergeCell ref="AV54:AX54"/>
     <mergeCell ref="A42:BQ42"/>
+    <mergeCell ref="AP57:AR57"/>
     <mergeCell ref="J30:P30"/>
     <mergeCell ref="AV41:AX41"/>
     <mergeCell ref="AE13:AF13"/>
     <mergeCell ref="AS45:AU45"/>
+    <mergeCell ref="BK57:BQ57"/>
     <mergeCell ref="AE40:AF40"/>
+    <mergeCell ref="X53:AD53"/>
     <mergeCell ref="X47:AD47"/>
     <mergeCell ref="Q19:W19"/>
     <mergeCell ref="AS38:AU38"/>
@@ -15245,18 +17400,26 @@
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AM13:AO13"/>
+    <mergeCell ref="AP52:AR52"/>
+    <mergeCell ref="X55:AD55"/>
     <mergeCell ref="AJ17:AL17"/>
+    <mergeCell ref="AM56:AO56"/>
+    <mergeCell ref="J54:P54"/>
     <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
     <mergeCell ref="Q44:W44"/>
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="J56:P56"/>
     <mergeCell ref="J43:P43"/>
+    <mergeCell ref="AM57:AO57"/>
     <mergeCell ref="X25:AD25"/>
     <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="E51:I51"/>
     <mergeCell ref="BK31:BQ31"/>
     <mergeCell ref="AG18:AI18"/>
     <mergeCell ref="BE17:BG17"/>
+    <mergeCell ref="B55:D55"/>
     <mergeCell ref="BB21:BD21"/>
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="AM25:AO25"/>
@@ -15282,15 +17445,17 @@
     <mergeCell ref="AM28:AO28"/>
     <mergeCell ref="BB18:BD18"/>
     <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="AV56:AX56"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE19 AE21:AE26 AE28:AE34 AE36:AE41 AE43:AE49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE19 AE21:AE26 AE28:AE34 AE36:AE41 AE43:AE49 AE51:AE57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG19 AG21:AG26 AG28:AG34 AG36:AG41 AG43:AG49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG19 AG21:AG26 AG28:AG34 AG36:AG41 AG43:AG49 AG51:AG57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV19 AV21:AV26 AV28:AV34 AV36:AV41 AV43:AV49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV19 AV21:AV26 AV28:AV34 AV36:AV41 AV43:AV49 AV51:AV57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
